--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0198.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0198.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Mẫu Tần số từ một Quả Cầu Sonoro... Ta sẽ giao nó cho đồng nghiệp. Cô ấy sẽ xử lý tốt hơn ta.</t>
+          <t>Mẫu Tần số từ một Sonoro Sphere... Ta sẽ giao nó cho đồng nghiệp. Cô ấy sẽ xử lý tốt hơn ta.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Giờ sao, không tin ta à?</t>
+          <t>Giờ sao, không tin tao à?</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{PlayerName}, có một nơi ta cần đến. Cậu đi cùng ta được không?</t>
+          <t>{PlayerName}, có một nơi tao cần đến. Cậu đi cùng tao được không?</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Giờ thì, nếu không còn gì khác, ta sẽ về phòng thí nghiệm đây.</t>
+          <t>Giờ thì, nếu không còn gì khác, tao sẽ về phòng thí nghiệm đây.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Ta nghe nói cậu và vị tướng đã cùng nhau giải quyết một vấn đề lớn.</t>
+          <t>Tao nghe nói cậu và vị tướng đã cùng nhau giải quyết một vấn đề lớn.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Nhiệm vụ gọi rồi. Ta phải quay về vị trí thôi. Gặp lại sau nhé!</t>
+          <t>Nhiệm vụ gọi rồi. Tao phải quay về vị trí thôi. Gặp lại sau nhé!</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Ta hứa.</t>
+          <t>Tao hứa.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Ta luyện tập lâu lắm rồi. Changfeng và mấy đứa kia cũng ngang ngửa nhau. Ngươi nghĩ sao—ta nên mở màn hay kết thúc ở vị trí chốt?</t>
+          <t>Tao luyện tập lâu lắm rồi. Changfeng và mấy đứa kia cũng ngang ngửa nhau. Mày nghĩ sao—tao nên mở màn hay kết thúc ở vị trí chốt?</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Không có gì... Có lẽ chỉ là do ta tưởng tượng thôi.</t>
+          <t>Không có gì... Có lẽ chỉ là do tao tưởng tượng thôi.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Tôi không nghe thấy gì cả! NÓI TO LÊN! Ngươi CÓ NGHE Ta KHÔNG!</t>
+          <t>Tôi không nghe thấy gì cả! NÓI TO LÊN! MÀY CÓ NGHE TAO KHÔNG!</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Ta nghe nói tất cả chúng ta phải quay về thành phố ngay. Thật à?</t>
+          <t>Tao nghe nói tất cả chúng ta phải quay về thành phố ngay. Thật à?</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Nói đùa thôi! Ta còn định chụp thêm vài tấm ảnh thằng cha trên con Gulpuff nữa cơ...</t>
+          <t>Nói đùa thôi! Tao còn định chụp thêm vài tấm ảnh thằng cha trên con Gulpuff nữa cơ...</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Ôi, được rồi. Nhưng ít nhất mình cũng có hai tấm ảnh tuyệt vời! Một tấm là Rover nổi tiếng dẫn đầu, còn tấm kia là một anh chàng cưỡi Gulpuff.</t>
+          <t>Ôi, được rồi. Nhưng ít nhất mình cũng có hai tấm ảnh tuyệt vời! Một tấm là Vận Mệnh Giả nổi tiếng dẫn đầu, còn tấm kia là một anh chàng cưỡi Gulpuff.</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Ta không bao giờ nói dối!</t>
+          <t>Tao không bao giờ nói dối!</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Rover là nhân chứng nhé! Móc tay nào!</t>
+          <t>Vận Mệnh Giả là nhân chứng nhé! Móc tay nào!</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ... những người đã ngã xuống vì Jinzhou sẽ muốn thấy nó hưng thịnh như thế nào bây giờ.</t>
+          <t>Tao cứ nghĩ... những người đã ngã xuống vì Jinzhou sẽ muốn thấy nó hưng thịnh như thế nào bây giờ.</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Ta hứa.</t>
+          <t>Tao hứa.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Hả? Lúc nào ta bị thương thế? Ta chả thấy gì cả.</t>
+          <t>Hả? Lúc nào tao bị thương thế? Tao chả thấy gì cả.</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Ta... người đầu tiên á? Thiệt hả?</t>
+          <t>Tao... người đầu tiên á? Thiệt hả?</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Chuẩn bị tinh thần đi, ta sẽ cho ngươi biết thế nào là thua cuộc đua</t>
+          <t>Chuẩn bị tinh thần đi, tao sẽ cho mày biết thế nào là thua cuộc đua</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Khi ta đến khu trao đổi, hãy lao thẳng vào mục tiêu và đừng ngoái lại. Phần còn lại ta lo.</t>
+          <t>Khi tao đến khu trao đổi, hãy lao thẳng vào mục tiêu và đừng ngoái lại. Phần còn lại tao lo.</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Suỵt! Đừng làm phiền {Male=anh ấy;Female=cô ấy}.</t>
+          <t>Suỵt! Đừng làm phiền {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Nói đơn giản, đó là ảo ảnh được tạo nên từ ký ức. Các học giả gọi nó là Quả Cầu Sonoro.</t>
+          <t>Nói đơn giản, đó là ảo ảnh được tạo nên từ ký ức. Các học giả gọi nó là Sonoro Sphere.</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Ta không thể diễn tả rõ ràng, nhưng có gì đó không ổn với bọn nó. Gần như là chúng…</t>
+          <t>Tao không thể diễn tả rõ ràng, nhưng có gì đó không ổn với bọn nó. Gần như là chúng…</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Thằng nhóc đó... Ta nhớ nó là tân binh mới! Khá lắm đấy!</t>
+          <t>Thằng nhóc đó... Tao nhớ nó là tân binh mới! Khá lắm đấy!</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Và không chỉ họ, còn nhiều người khác đã bỏ mạng tại Cao Nguyên Desorock.</t>
+          <t>Và không chỉ họ, còn nhiều người khác đã bỏ mạng tại Desorock Highland.</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Ngươi mời ta vào đội tạm thời để Ganquan và Lingyan vẫn có thể tham gia cuộc đua.</t>
+          <t>Mày mời tao vào đội tạm thời để Ganquan và Lingyan vẫn có thể tham gia cuộc đua.</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>...Sau trận chiến ở Cao nguyên Desorock à?</t>
+          <t>...Sau trận chiến ở Desorock Highland à?</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Nếu phải ở lại giữ trận địa, tính cả ta vào. Không thể để lũ quái vật chiếm chỗ này được.</t>
+          <t>Nếu phải ở lại giữ trận địa, tính cả tao vào. Không thể để lũ quái vật chiếm chỗ này được.</t>
         </is>
       </c>
     </row>
